--- a/diseases/d019/2000-2004.xlsx
+++ b/diseases/d019/2000-2004.xlsx
@@ -1169,6 +1169,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1556,6 +1561,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1704,6 +1714,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1852,6 +1867,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2000,6 +2020,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2148,6 +2173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2296,6 +2326,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2444,6 +2479,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2592,6 +2632,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2740,6 +2785,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2888,6 +2938,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3036,6 +3091,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3577,6 +3637,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3961,6 +4026,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4109,6 +4179,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4254,6 +4329,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4402,6 +4482,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4547,6 +4632,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4695,6 +4785,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4840,6 +4935,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4988,6 +5088,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5133,6 +5238,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5281,6 +5391,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5426,6 +5541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5574,6 +5694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5719,6 +5844,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5867,6 +5997,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6012,6 +6147,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6160,6 +6300,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6305,6 +6450,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6453,6 +6603,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6598,6 +6753,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6746,6 +6906,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6891,6 +7056,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7039,6 +7209,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7184,6 +7359,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7725,6 +7905,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8109,6 +8294,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8257,6 +8447,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8402,6 +8597,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8550,6 +8750,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8695,6 +8900,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8843,6 +9053,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8988,6 +9203,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9136,6 +9356,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9281,6 +9506,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9429,6 +9659,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9574,6 +9809,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9722,6 +9962,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9867,6 +10112,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10015,6 +10265,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10160,6 +10415,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10308,6 +10568,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10453,6 +10718,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10601,6 +10871,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10746,6 +11021,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10894,6 +11174,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11039,6 +11324,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11187,6 +11477,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11332,6 +11627,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11873,6 +12173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12257,6 +12562,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12405,6 +12715,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12550,6 +12865,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12698,6 +13018,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12843,6 +13168,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12991,6 +13321,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13136,6 +13471,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13284,6 +13624,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13429,6 +13774,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13577,6 +13927,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13722,6 +14077,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13870,6 +14230,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14015,6 +14380,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14163,6 +14533,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14308,6 +14683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14456,6 +14836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14601,6 +14986,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14749,6 +15139,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14894,6 +15289,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15042,6 +15442,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15187,6 +15592,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15335,6 +15745,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15480,6 +15895,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16021,6 +16441,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16405,6 +16830,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16553,6 +16983,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16698,6 +17133,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16846,6 +17286,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16991,6 +17436,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17139,6 +17589,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17284,6 +17739,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17432,6 +17892,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17577,6 +18042,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17725,6 +18195,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17870,6 +18345,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18018,6 +18498,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18163,6 +18648,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18311,6 +18801,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18456,6 +18951,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18604,6 +19104,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18749,6 +19254,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18897,6 +19407,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19042,6 +19557,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19190,6 +19710,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19335,6 +19860,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19483,6 +20013,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19626,6 +20161,11 @@
       <c r="S124" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">

--- a/diseases/d019/2000-2004.xlsx
+++ b/diseases/d019/2000-2004.xlsx
@@ -18135,17 +18135,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -18170,98 +18170,182 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2004-05-10</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
-      <c r="R111" t="n">
-        <v>0</v>
-      </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="P111" t="n">
+        <v>1</v>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>__source_native__</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>national_ifsG_notification_registry</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>DE_RKI_SURVSTAT_source_native</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN111" t="b">
+        <v>0</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_RABI_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -18288,17 +18372,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>DE-BB</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Brandenburg, Germany</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -18323,95 +18407,175 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2004-05-10</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" t="n">
-        <v>0</v>
-      </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>tollwut</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>Tollwut</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>country:DE-BB:national</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL112" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN112" t="b">
+        <v>0</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18438,17 +18602,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE-BE</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Berlin, Germany</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -18473,98 +18637,175 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2004-05-10</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
-      <c r="R113" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>tollwut</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>Tollwut</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>country:DE-BE:national</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL113" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN113" t="b">
+        <v>0</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18591,17 +18832,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>DE-BW</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Baden-Württemberg, Germany</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -18626,95 +18867,175 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2004-05-10</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
-      </c>
-      <c r="R114" t="n">
-        <v>0</v>
-      </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>tollwut</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>Tollwut</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>country:DE-BW:national</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL114" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN114" t="b">
+        <v>0</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18741,17 +19062,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE-BY</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Bayern, Germany</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -18776,98 +19097,175 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2004-05-10</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2004-08</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
-      <c r="R115" t="n">
-        <v>0</v>
-      </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>tollwut</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>Tollwut</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>country:DE-BY:national</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL115" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN115" t="b">
+        <v>0</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18894,17 +19292,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>DE-HB</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Bremen, Germany</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -18929,95 +19327,175 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2004-05-10</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2004-08</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="R116" t="n">
-        <v>0</v>
-      </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>tollwut</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>Tollwut</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>country:DE-HB:national</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL116" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN116" t="b">
+        <v>0</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19044,17 +19522,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE-HE</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Hessen, Germany</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -19079,98 +19557,175 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2004-09-01</t>
+          <t>2004-05-10</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2004-09</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
-      <c r="R117" t="n">
-        <v>0</v>
-      </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>tollwut</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>Tollwut</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>country:DE-HE:national</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL117" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN117" t="b">
+        <v>0</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19197,17 +19752,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>DE-HH</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hamburg, Germany</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -19232,95 +19787,175 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2004-09-01</t>
+          <t>2004-05-10</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2004-09</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O118" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>tollwut</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Tollwut</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>country:DE-HH:national</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL118" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN118" t="b">
+        <v>0</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19347,17 +19982,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE-MV</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Mecklenburg-Vorpommern, Germany</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -19382,98 +20017,175 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2004-10-01</t>
+          <t>2004-05-10</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2004-10</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
-      <c r="R119" t="n">
-        <v>0</v>
-      </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>tollwut</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>Tollwut</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>country:DE-MV:national</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL119" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN119" t="b">
+        <v>0</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19500,17 +20212,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>DE-NI</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Niedersachsen, Germany</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -19535,95 +20247,175 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2004-10-01</t>
+          <t>2004-05-10</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2004-10</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
-      </c>
-      <c r="R120" t="n">
-        <v>0</v>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>tollwut</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>Tollwut</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>country:DE-NI:national</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL120" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN120" t="b">
+        <v>0</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19650,17 +20442,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE-NW</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Nordrhein-Westfalen, Germany</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -19685,98 +20477,175 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2004-11-01</t>
+          <t>2004-05-10</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2004-11</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>tollwut</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>Tollwut</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>country:DE-NW:national</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL121" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN121" t="b">
+        <v>0</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19803,17 +20672,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>DE-RP</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Rheinland-Pfalz, Germany</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -19838,95 +20707,175 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2004-11-01</t>
+          <t>2004-05-10</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2004-11</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>tollwut</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>Tollwut</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>country:DE-RP:national</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL122" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN122" t="b">
+        <v>0</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19953,17 +20902,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE-SH</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Schleswig-Holstein, Germany</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -19988,98 +20937,175 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-05-10</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
-      <c r="R123" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>tollwut</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Tollwut</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:DE-SH:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL123" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>0</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20106,17 +21132,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>DE-SL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Saarland, Germany</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -20141,93 +21167,2984 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-05-10</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
-      </c>
-      <c r="R124" t="n">
-        <v>0</v>
-      </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>tollwut</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>Tollwut</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>country:DE-SL:national</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL124" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN124" t="b">
+        <v>0</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>DE-SN</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Sachsen, Germany</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2004-05-10</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2004-05</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" t="n">
+        <v>1</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>tollwut</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Tollwut</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>country:DE-SN:national</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL125" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
+      <c r="AT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>DE-ST</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Sachsen-Anhalt, Germany</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2004-05-10</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2004-05</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>1</v>
+      </c>
+      <c r="O126" t="n">
+        <v>1</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>tollwut</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>Tollwut</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>country:DE-ST:national</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL126" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr"/>
+      <c r="AT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>DE-TH</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Thüringen, Germany</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2004-05-10</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2004-05</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>1</v>
+      </c>
+      <c r="O127" t="n">
+        <v>1</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>tollwut</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Tollwut</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:DE-TH:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL127" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
+      <c r="AT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2004-06-01</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2004-06</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr"/>
+      <c r="AT128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV124" t="inlineStr">
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2004-06-01</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2004-06</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr"/>
+      <c r="AT129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW124" t="inlineStr">
+      <c r="AW129" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
+      <c r="AX129" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY124" t="inlineStr">
+      <c r="AY129" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ124" t="inlineStr">
+      <c r="AZ129" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA124" t="inlineStr">
+      <c r="BA129" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB124" t="inlineStr">
+      <c r="BB129" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC124" t="inlineStr">
+      <c r="BC129" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2004-07-01</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2004-07</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr"/>
+      <c r="AT130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2004-07-01</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2004-07</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr"/>
+      <c r="AT131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2004-08-01</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2004-08</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr"/>
+      <c r="AT132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2004-08-01</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2004-08</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP133" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr"/>
+      <c r="AT133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2004-09-01</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2004-09</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr"/>
+      <c r="AT134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC134" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2004-09-01</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2004-09</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr"/>
+      <c r="AT135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA135" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC135" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2004-10-01</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2004-10</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr"/>
+      <c r="AT136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC136" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2004-10-01</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2004-10</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr"/>
+      <c r="AT137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA137" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC137" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2004-11-01</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2004-11</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP138" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr"/>
+      <c r="AT138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA138" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB138" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC138" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2004-11-01</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2004-11</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr"/>
+      <c r="AT139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2004-12</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP140" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr"/>
+      <c r="AT140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV140" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA140" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC140" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2004-12</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr"/>
+      <c r="AT141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA141" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC141" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -20359,7 +24276,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -20379,7 +24296,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -20389,7 +24306,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d019/2000-2004.xlsx
+++ b/diseases/d019/2000-2004.xlsx
@@ -18372,17 +18372,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>DE-BB</t>
+          <t>DE-BY</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Brandenburg, Germany</t>
+          <t>Bayern, Germany</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -18421,121 +18421,47 @@
       <c r="O112" t="n">
         <v>1</v>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U112" t="inlineStr">
         <is>
           <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
         </is>
       </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>tollwut</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>Tollwut</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>country:DE-BB:national</t>
-        </is>
-      </c>
-      <c r="AD112" t="inlineStr">
-        <is>
-          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
-        </is>
-      </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG112" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL112" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN112" t="b">
-        <v>0</v>
-      </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
+      </c>
       <c r="AT112" t="n">
         <v>1</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
@@ -18607,12 +18533,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>DE-BE</t>
+          <t>DE-BY</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Berlin, Germany</t>
+          <t>Bayern, Germany</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -18693,12 +18619,12 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>country:DE-BE:national</t>
+          <t>country:DE-BY:national</t>
         </is>
       </c>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AE113" t="inlineStr">
@@ -18742,30 +18668,34 @@
         </is>
       </c>
       <c r="AN113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
+      </c>
       <c r="AT113" t="n">
         <v>1</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
@@ -18832,17 +18762,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>DE-BW</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Baden-Württemberg, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -18867,175 +18797,98 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2004-05-10</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>1</v>
-      </c>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
-        </is>
-      </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>tollwut</t>
-        </is>
-      </c>
-      <c r="W114" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X114" t="inlineStr">
-        <is>
-          <t>Tollwut</t>
-        </is>
-      </c>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>country:DE-BW:national</t>
-        </is>
-      </c>
-      <c r="AD114" t="inlineStr">
-        <is>
-          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
-        </is>
-      </c>
-      <c r="AE114" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF114" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG114" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL114" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN114" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ114" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -19062,17 +18915,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>DE-BY</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Bayern, Germany</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -19097,175 +18950,95 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2004-05-10</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>1</v>
-      </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
-        </is>
-      </c>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>tollwut</t>
-        </is>
-      </c>
-      <c r="W115" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X115" t="inlineStr">
-        <is>
-          <t>Tollwut</t>
-        </is>
-      </c>
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>country:DE-BY:national</t>
-        </is>
-      </c>
-      <c r="AD115" t="inlineStr">
-        <is>
-          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
-        </is>
-      </c>
-      <c r="AE115" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF115" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG115" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL115" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN115" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -19292,17 +19065,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>DE-HB</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Bremen, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -19327,175 +19100,98 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2004-05-10</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="N116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>1</v>
-      </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
-        </is>
-      </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>tollwut</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X116" t="inlineStr">
-        <is>
-          <t>Tollwut</t>
-        </is>
-      </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>country:DE-HB:national</t>
-        </is>
-      </c>
-      <c r="AD116" t="inlineStr">
-        <is>
-          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
-        </is>
-      </c>
-      <c r="AE116" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF116" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG116" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL116" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN116" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -19522,17 +19218,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>DE-HE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hessen, Germany</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -19557,175 +19253,95 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2004-05-10</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="N117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
-        <v>1</v>
-      </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
-        </is>
-      </c>
-      <c r="V117" t="inlineStr">
-        <is>
-          <t>tollwut</t>
-        </is>
-      </c>
-      <c r="W117" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X117" t="inlineStr">
-        <is>
-          <t>Tollwut</t>
-        </is>
-      </c>
-      <c r="Y117" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>country:DE-HE:national</t>
-        </is>
-      </c>
-      <c r="AD117" t="inlineStr">
-        <is>
-          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
-        </is>
-      </c>
-      <c r="AE117" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF117" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG117" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL117" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN117" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ117" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -19752,17 +19368,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>DE-HH</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hamburg, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -19787,175 +19403,98 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2004-05-10</t>
+          <t>2004-08-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-08</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>1</v>
-      </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
-        </is>
-      </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>tollwut</t>
-        </is>
-      </c>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>Tollwut</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>country:DE-HH:national</t>
-        </is>
-      </c>
-      <c r="AD118" t="inlineStr">
-        <is>
-          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
-        </is>
-      </c>
-      <c r="AE118" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF118" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG118" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL118" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN118" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -19982,17 +19521,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>DE-MV</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Mecklenburg-Vorpommern, Germany</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -20017,175 +19556,95 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2004-05-10</t>
+          <t>2004-08-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-08</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>1</v>
-      </c>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
-        </is>
-      </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>tollwut</t>
-        </is>
-      </c>
-      <c r="W119" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X119" t="inlineStr">
-        <is>
-          <t>Tollwut</t>
-        </is>
-      </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>country:DE-MV:national</t>
-        </is>
-      </c>
-      <c r="AD119" t="inlineStr">
-        <is>
-          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
-        </is>
-      </c>
-      <c r="AE119" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF119" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG119" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL119" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN119" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20212,17 +19671,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>DE-NI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Niedersachsen, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -20247,175 +19706,98 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2004-05-10</t>
+          <t>2004-09-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-09</t>
         </is>
       </c>
       <c r="N120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>1</v>
-      </c>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>tollwut</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X120" t="inlineStr">
-        <is>
-          <t>Tollwut</t>
-        </is>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>country:DE-NI:national</t>
-        </is>
-      </c>
-      <c r="AD120" t="inlineStr">
-        <is>
-          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
-        </is>
-      </c>
-      <c r="AE120" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF120" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG120" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL120" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN120" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -20442,17 +19824,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>DE-NW</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nordrhein-Westfalen, Germany</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -20477,175 +19859,95 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2004-05-10</t>
+          <t>2004-09-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-09</t>
         </is>
       </c>
       <c r="N121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>1</v>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>tollwut</t>
-        </is>
-      </c>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X121" t="inlineStr">
-        <is>
-          <t>Tollwut</t>
-        </is>
-      </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>country:DE-NW:national</t>
-        </is>
-      </c>
-      <c r="AD121" t="inlineStr">
-        <is>
-          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
-        </is>
-      </c>
-      <c r="AE121" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF121" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG121" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL121" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN121" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20672,17 +19974,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>DE-RP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -20707,175 +20009,98 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2004-05-10</t>
+          <t>2004-10-01</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-10</t>
         </is>
       </c>
       <c r="N122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>1</v>
-      </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
-        </is>
-      </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>tollwut</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>Tollwut</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>country:DE-RP:national</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
-        <is>
-          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
-        </is>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG122" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL122" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN122" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -20902,17 +20127,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>DE-SH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Schleswig-Holstein, Germany</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -20937,175 +20162,95 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2004-05-10</t>
+          <t>2004-10-01</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-10</t>
         </is>
       </c>
       <c r="N123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>1</v>
-      </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
-        </is>
-      </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>tollwut</t>
-        </is>
-      </c>
-      <c r="W123" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X123" t="inlineStr">
-        <is>
-          <t>Tollwut</t>
-        </is>
-      </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>country:DE-SH:national</t>
-        </is>
-      </c>
-      <c r="AD123" t="inlineStr">
-        <is>
-          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
-        </is>
-      </c>
-      <c r="AE123" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF123" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG123" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL123" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN123" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -21132,17 +20277,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>DE-SL</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Saarland, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21167,175 +20312,98 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2004-05-10</t>
+          <t>2004-11-01</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-11</t>
         </is>
       </c>
       <c r="N124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>1</v>
-      </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
-        </is>
-      </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>tollwut</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X124" t="inlineStr">
-        <is>
-          <t>Tollwut</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>country:DE-SL:national</t>
-        </is>
-      </c>
-      <c r="AD124" t="inlineStr">
-        <is>
-          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
-        </is>
-      </c>
-      <c r="AE124" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF124" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG124" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL124" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN124" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -21362,17 +20430,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -21397,175 +20465,95 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2004-05-10</t>
+          <t>2004-11-01</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-11</t>
         </is>
       </c>
       <c r="N125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>1</v>
-      </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>tollwut</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t>Tollwut</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>country:DE-SN:national</t>
-        </is>
-      </c>
-      <c r="AD125" t="inlineStr">
-        <is>
-          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
-        </is>
-      </c>
-      <c r="AE125" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF125" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG125" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL125" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN125" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -21592,17 +20580,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>DE-ST</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Sachsen-Anhalt, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -21627,175 +20615,98 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2004-05-10</t>
+          <t>2004-12-01</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-12</t>
         </is>
       </c>
       <c r="N126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>1</v>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
-        </is>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>tollwut</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>Tollwut</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>country:DE-ST:national</t>
-        </is>
-      </c>
-      <c r="AD126" t="inlineStr">
-        <is>
-          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
-        </is>
-      </c>
-      <c r="AE126" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG126" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL126" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN126" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -21822,17 +20733,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>DE-TH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Thüringen, Germany</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -21857,2294 +20768,93 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2004-05-10</t>
+          <t>2004-12-01</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-12</t>
         </is>
       </c>
       <c r="N127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>1</v>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>tollwut</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X127" t="inlineStr">
-        <is>
-          <t>Tollwut</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>country:DE-TH:national</t>
-        </is>
-      </c>
-      <c r="AD127" t="inlineStr">
-        <is>
-          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
-        </is>
-      </c>
-      <c r="AE127" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF127" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG127" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL127" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN127" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>rabies</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>狂犬病</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>2004-06-01</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>2004-06</t>
-        </is>
-      </c>
-      <c r="N128" t="n">
-        <v>0</v>
-      </c>
-      <c r="O128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
-      <c r="R128" t="n">
-        <v>0</v>
-      </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO128" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP128" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr"/>
-      <c r="AT128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV128" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW128" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY128" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ128" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA128" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB128" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC128" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>rabies</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>狂犬病</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>2004-06-01</t>
-        </is>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>2004-06</t>
-        </is>
-      </c>
-      <c r="N129" t="n">
-        <v>0</v>
-      </c>
-      <c r="O129" t="n">
-        <v>0</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA129" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP129" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr"/>
-      <c r="AT129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV129" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW129" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ129" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA129" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB129" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC129" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>rabies</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>狂犬病</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>2004-07-01</t>
-        </is>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>2004-07</t>
-        </is>
-      </c>
-      <c r="N130" t="n">
-        <v>0</v>
-      </c>
-      <c r="O130" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
-      <c r="R130" t="n">
-        <v>0</v>
-      </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP130" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr"/>
-      <c r="AT130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV130" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW130" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ130" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA130" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB130" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC130" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>rabies</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>狂犬病</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>2004-07-01</t>
-        </is>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>2004-07</t>
-        </is>
-      </c>
-      <c r="N131" t="n">
-        <v>0</v>
-      </c>
-      <c r="O131" t="n">
-        <v>0</v>
-      </c>
-      <c r="R131" t="n">
-        <v>0</v>
-      </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP131" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
-      <c r="AT131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV131" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW131" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ131" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA131" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB131" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC131" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>rabies</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>狂犬病</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>2004-08-01</t>
-        </is>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>2004-08</t>
-        </is>
-      </c>
-      <c r="N132" t="n">
-        <v>0</v>
-      </c>
-      <c r="O132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
-      <c r="R132" t="n">
-        <v>0</v>
-      </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA132" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP132" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr"/>
-      <c r="AT132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV132" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW132" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY132" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ132" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA132" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB132" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC132" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>rabies</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>狂犬病</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>2004-08-01</t>
-        </is>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>2004-08</t>
-        </is>
-      </c>
-      <c r="N133" t="n">
-        <v>0</v>
-      </c>
-      <c r="O133" t="n">
-        <v>0</v>
-      </c>
-      <c r="R133" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP133" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr"/>
-      <c r="AT133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV133" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW133" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY133" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ133" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA133" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB133" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC133" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>rabies</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>狂犬病</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>2004-09-01</t>
-        </is>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>2004-09</t>
-        </is>
-      </c>
-      <c r="N134" t="n">
-        <v>0</v>
-      </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
-      <c r="R134" t="n">
-        <v>0</v>
-      </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP134" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr"/>
-      <c r="AT134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV134" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW134" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX134" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY134" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ134" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA134" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB134" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC134" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>rabies</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>狂犬病</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>2004-09-01</t>
-        </is>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>2004-09</t>
-        </is>
-      </c>
-      <c r="N135" t="n">
-        <v>0</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP135" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr"/>
-      <c r="AT135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV135" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW135" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX135" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY135" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ135" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA135" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB135" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC135" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>rabies</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>狂犬病</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>2004-10-01</t>
-        </is>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>2004-10</t>
-        </is>
-      </c>
-      <c r="N136" t="n">
-        <v>0</v>
-      </c>
-      <c r="O136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
-      <c r="R136" t="n">
-        <v>0</v>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP136" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr"/>
-      <c r="AT136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV136" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW136" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX136" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY136" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ136" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA136" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB136" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC136" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>rabies</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>狂犬病</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>2004-10-01</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>2004-10</t>
-        </is>
-      </c>
-      <c r="N137" t="n">
-        <v>0</v>
-      </c>
-      <c r="O137" t="n">
-        <v>0</v>
-      </c>
-      <c r="R137" t="n">
-        <v>0</v>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP137" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr"/>
-      <c r="AT137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV137" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW137" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX137" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY137" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ137" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA137" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB137" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC137" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>rabies</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>狂犬病</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>2004-11-01</t>
-        </is>
-      </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>2004-11</t>
-        </is>
-      </c>
-      <c r="N138" t="n">
-        <v>0</v>
-      </c>
-      <c r="O138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0</v>
-      </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA138" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO138" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP138" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr"/>
-      <c r="AT138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV138" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW138" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX138" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY138" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ138" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA138" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB138" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC138" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>rabies</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>狂犬病</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>2004-11-01</t>
-        </is>
-      </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>2004-11</t>
-        </is>
-      </c>
-      <c r="N139" t="n">
-        <v>0</v>
-      </c>
-      <c r="O139" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA139" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP139" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr"/>
-      <c r="AT139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV139" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW139" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX139" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY139" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ139" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA139" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB139" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC139" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>rabies</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>狂犬病</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t>2004-12-01</t>
-        </is>
-      </c>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>2004-12</t>
-        </is>
-      </c>
-      <c r="N140" t="n">
-        <v>0</v>
-      </c>
-      <c r="O140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP140" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr"/>
-      <c r="AT140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV140" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW140" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX140" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY140" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ140" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA140" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB140" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC140" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>rabies</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>狂犬病</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>2004-12-01</t>
-        </is>
-      </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>2004-12</t>
-        </is>
-      </c>
-      <c r="N141" t="n">
-        <v>0</v>
-      </c>
-      <c r="O141" t="n">
-        <v>0</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0</v>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA141" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO141" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP141" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr"/>
-      <c r="AT141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV141" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW141" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX141" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY141" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ141" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA141" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB141" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC141" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -24266,7 +20976,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
@@ -24276,7 +20986,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>140</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">
@@ -24296,7 +21006,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -24328,7 +21038,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d019/2000-2004.xlsx
+++ b/diseases/d019/2000-2004.xlsx
@@ -1247,17 +1247,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2000-02-01</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2000-02</t>
+          <t>2000-01</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1296,69 +1296,170 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Hundaæði</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
+        <v>0</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_RABI_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1521,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2000-03-01</t>
+          <t>2000-02-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2000-03</t>
+          <t>2000-02</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1558,12 +1659,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2000-04-01</t>
+          <t>2000-03-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2000-04</t>
+          <t>2000-03</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1696,12 +1797,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2000-05-01</t>
+          <t>2000-04-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2000-05</t>
+          <t>2000-04</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1834,12 +1935,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2000-06-01</t>
+          <t>2000-05-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2000-06</t>
+          <t>2000-05</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1972,12 +2073,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2000-07-01</t>
+          <t>2000-06-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2000-07</t>
+          <t>2000-06</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2110,12 +2211,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2000-08-01</t>
+          <t>2000-07-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2000-08</t>
+          <t>2000-07</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2248,12 +2349,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2000-09-01</t>
+          <t>2000-08-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2000-09</t>
+          <t>2000-08</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2386,12 +2487,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2000-10-01</t>
+          <t>2000-09-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2000-10</t>
+          <t>2000-09</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2524,12 +2625,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2000-11-01</t>
+          <t>2000-10-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2000-11</t>
+          <t>2000-10</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2662,12 +2763,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2000-12-01</t>
+          <t>2000-11-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2000-12</t>
+          <t>2000-11</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2770,12 +2871,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2800,12 +2901,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2000-12-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2001-01</t>
+          <t>2000-12</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -2814,90 +2915,69 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -2924,7 +3004,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2973,98 +3053,23 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN17" t="b">
-        <v>1</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -3158,17 +3163,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3207,69 +3212,165 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN18" t="b">
+        <v>1</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3301,12 +3402,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3343,6 +3444,9 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
@@ -3369,42 +3473,42 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -3431,17 +3535,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3466,12 +3570,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2001-02-01</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2001-02</t>
+          <t>2001-01</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3480,69 +3584,170 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Hundaæði</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN20" t="b">
+        <v>0</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr"/>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_RABI_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -3604,12 +3809,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2001-02-01</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2001-02</t>
+          <t>2001-01</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -3739,12 +3944,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2001-03-01</t>
+          <t>2001-02-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2001-03</t>
+          <t>2001-02</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -3877,12 +4082,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2001-03-01</t>
+          <t>2001-02-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2001-03</t>
+          <t>2001-02</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4012,12 +4217,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2001-04-01</t>
+          <t>2001-03-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2001-04</t>
+          <t>2001-03</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -4150,12 +4355,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2001-04-01</t>
+          <t>2001-03-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2001-04</t>
+          <t>2001-03</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4285,12 +4490,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2001-05-01</t>
+          <t>2001-04-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2001-05</t>
+          <t>2001-04</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4423,12 +4628,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2001-05-01</t>
+          <t>2001-04-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2001-05</t>
+          <t>2001-04</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4558,12 +4763,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2001-06-01</t>
+          <t>2001-05-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2001-06</t>
+          <t>2001-05</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -4696,12 +4901,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2001-06-01</t>
+          <t>2001-05-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2001-06</t>
+          <t>2001-05</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -4831,12 +5036,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2001-07-01</t>
+          <t>2001-06-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2001-07</t>
+          <t>2001-06</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -4969,12 +5174,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2001-07-01</t>
+          <t>2001-06-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2001-07</t>
+          <t>2001-06</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -5104,12 +5309,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2001-08-01</t>
+          <t>2001-07-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2001-08</t>
+          <t>2001-07</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -5242,12 +5447,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2001-08-01</t>
+          <t>2001-07-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2001-08</t>
+          <t>2001-07</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5377,12 +5582,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2001-09-01</t>
+          <t>2001-08-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2001-09</t>
+          <t>2001-08</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -5515,12 +5720,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2001-09-01</t>
+          <t>2001-08-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2001-09</t>
+          <t>2001-08</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -5650,25 +5855,25 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2001-10-01</t>
+          <t>2001-09-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2001-10</t>
+          <t>2001-09</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0.01476180680677245</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
@@ -5788,12 +5993,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2001-10-01</t>
+          <t>2001-09-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2001-10</t>
+          <t>2001-09</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -5923,25 +6128,25 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2001-11-01</t>
+          <t>2001-10-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2001-11</t>
+          <t>2001-10</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>0.01476180680677245</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -6061,12 +6266,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2001-11-01</t>
+          <t>2001-10-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2001-11</t>
+          <t>2001-10</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6196,12 +6401,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2001-12-01</t>
+          <t>2001-11-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2001-12</t>
+          <t>2001-11</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6334,22 +6539,22 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2001-12-01</t>
+          <t>2001-11-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2001-12</t>
+          <t>2001-11</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0.002125693624458129</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -6439,12 +6644,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6469,12 +6674,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2001-12-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2001-12</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -6483,90 +6688,69 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ42" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS42" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -6593,17 +6777,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6628,179 +6812,80 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2001-12-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2001-12</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.002125693624458129</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG43" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN43" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ43" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS43" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -6832,12 +6917,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6876,69 +6961,90 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6965,17 +7071,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7014,66 +7120,165 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="R45" t="n">
-        <v>0</v>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN45" t="b">
+        <v>1</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7135,12 +7340,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2002-02-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2002-02</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7238,17 +7443,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7273,12 +7478,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2002-02-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2002-02</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7287,66 +7492,170 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="R47" t="n">
-        <v>0</v>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Hundaæði</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN47" t="b">
+        <v>0</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr"/>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_RABI_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -7378,12 +7687,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7408,21 +7717,18 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2002-03-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2002-03</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
@@ -7449,42 +7755,42 @@
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7516,12 +7822,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7546,18 +7852,21 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2002-03-01</t>
+          <t>2002-02-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2002-03</t>
+          <t>2002-02</t>
         </is>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
@@ -7584,42 +7893,42 @@
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7651,12 +7960,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7681,21 +7990,18 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2002-04-01</t>
+          <t>2002-02-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2002-02</t>
         </is>
       </c>
       <c r="N50" t="n">
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
@@ -7722,42 +8028,42 @@
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7789,12 +8095,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7819,18 +8125,21 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2002-04-01</t>
+          <t>2002-03-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2002-03</t>
         </is>
       </c>
       <c r="N51" t="n">
         <v>0</v>
       </c>
       <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
@@ -7857,42 +8166,42 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7924,12 +8233,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7954,21 +8263,18 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2002-05-01</t>
+          <t>2002-03-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2002-05</t>
+          <t>2002-03</t>
         </is>
       </c>
       <c r="N52" t="n">
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
@@ -7995,42 +8301,42 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8368,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8092,18 +8398,21 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2002-05-01</t>
+          <t>2002-04-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2002-05</t>
+          <t>2002-04</t>
         </is>
       </c>
       <c r="N53" t="n">
         <v>0</v>
       </c>
       <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
@@ -8130,42 +8439,42 @@
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8197,12 +8506,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8227,21 +8536,18 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2002-06-01</t>
+          <t>2002-04-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2002-06</t>
+          <t>2002-04</t>
         </is>
       </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
@@ -8268,42 +8574,42 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8335,12 +8641,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8365,22 +8671,25 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2002-06-01</t>
+          <t>2002-05-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2002-06</t>
+          <t>2002-05</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0.002114204216545633</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -8403,42 +8712,42 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8779,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8500,21 +8809,18 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2002-07-01</t>
+          <t>2002-05-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2002-07</t>
+          <t>2002-05</t>
         </is>
       </c>
       <c r="N56" t="n">
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
@@ -8541,42 +8847,42 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8608,12 +8914,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8638,18 +8944,21 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2002-07-01</t>
+          <t>2002-06-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2002-07</t>
+          <t>2002-06</t>
         </is>
       </c>
       <c r="N57" t="n">
         <v>0</v>
       </c>
       <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
@@ -8676,42 +8985,42 @@
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8743,12 +9052,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -8773,25 +9082,22 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2002-08-01</t>
+          <t>2002-06-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2002-08</t>
+          <t>2002-06</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>0.002114204216545633</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -8814,42 +9120,42 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8881,12 +9187,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -8911,18 +9217,21 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2002-08-01</t>
+          <t>2002-07-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2002-08</t>
+          <t>2002-07</t>
         </is>
       </c>
       <c r="N59" t="n">
         <v>0</v>
       </c>
       <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
@@ -8949,42 +9258,42 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9016,12 +9325,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9046,21 +9355,18 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2002-09-01</t>
+          <t>2002-07-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2002-09</t>
+          <t>2002-07</t>
         </is>
       </c>
       <c r="N60" t="n">
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
@@ -9087,42 +9393,42 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -9154,12 +9460,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9184,18 +9490,21 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2002-09-01</t>
+          <t>2002-08-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2002-09</t>
+          <t>2002-08</t>
         </is>
       </c>
       <c r="N61" t="n">
         <v>0</v>
       </c>
       <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
@@ -9222,42 +9531,42 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9289,12 +9598,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -9319,21 +9628,18 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2002-10-01</t>
+          <t>2002-08-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2002-10</t>
+          <t>2002-08</t>
         </is>
       </c>
       <c r="N62" t="n">
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
@@ -9360,42 +9666,42 @@
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -9427,12 +9733,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -9457,18 +9763,21 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2002-10-01</t>
+          <t>2002-09-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2002-10</t>
+          <t>2002-09</t>
         </is>
       </c>
       <c r="N63" t="n">
         <v>0</v>
       </c>
       <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
@@ -9495,42 +9804,42 @@
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9562,12 +9871,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -9592,21 +9901,18 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2002-11-01</t>
+          <t>2002-09-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2002-11</t>
+          <t>2002-09</t>
         </is>
       </c>
       <c r="N64" t="n">
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
@@ -9633,42 +9939,42 @@
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -9700,12 +10006,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -9730,18 +10036,21 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2002-11-01</t>
+          <t>2002-10-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2002-11</t>
+          <t>2002-10</t>
         </is>
       </c>
       <c r="N65" t="n">
         <v>0</v>
       </c>
       <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
@@ -9768,42 +10077,42 @@
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9835,12 +10144,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -9865,21 +10174,18 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2002-10-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2002-12</t>
+          <t>2002-10</t>
         </is>
       </c>
       <c r="N66" t="n">
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
@@ -9906,42 +10212,42 @@
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -9973,12 +10279,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10003,18 +10309,21 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2002-11-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2002-12</t>
+          <t>2002-11</t>
         </is>
       </c>
       <c r="N67" t="n">
         <v>0</v>
       </c>
       <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
@@ -10041,42 +10350,42 @@
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10108,12 +10417,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -10138,104 +10447,80 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2002-11-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2002-11</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>0.00314105057210781</v>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -10262,17 +10547,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -10297,179 +10582,83 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2002-12-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2002-12</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>1</v>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD69" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE69" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG69" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN69" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ69" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS69" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10501,12 +10690,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -10531,21 +10720,18 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2002-12-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2002-12</t>
         </is>
       </c>
       <c r="N70" t="n">
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
@@ -10572,42 +10758,42 @@
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -10639,12 +10825,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -10678,71 +10864,95 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>0.00314105057210781</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT71" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -10769,17 +10979,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -10804,83 +11014,179 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2003-02-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2003-02</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN72" t="b">
+        <v>1</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT72" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -10912,12 +11218,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -10942,22 +11248,25 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2003-02-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2003-02</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>0.002104635732751713</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
@@ -10980,42 +11289,42 @@
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11042,17 +11351,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11077,12 +11386,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2003-03-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2003-03</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -11091,69 +11400,170 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0</v>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Hundaæði</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN74" t="b">
+        <v>0</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr"/>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_RABI_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT74" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11625,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2003-03-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2003-03</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -11350,12 +11760,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2003-04-01</t>
+          <t>2003-02-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2003-04</t>
+          <t>2003-02</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -11488,22 +11898,22 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2003-04-01</t>
+          <t>2003-02-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2003-04</t>
+          <t>2003-02</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>0.002104635732751713</v>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
@@ -11623,12 +12033,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2003-05-01</t>
+          <t>2003-03-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2003-05</t>
+          <t>2003-03</t>
         </is>
       </c>
       <c r="N78" t="n">
@@ -11761,22 +12171,22 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2003-05-01</t>
+          <t>2003-03-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2003-05</t>
+          <t>2003-03</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>0.002104635732751713</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
@@ -11896,12 +12306,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2003-06-01</t>
+          <t>2003-04-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2003-06</t>
+          <t>2003-04</t>
         </is>
       </c>
       <c r="N80" t="n">
@@ -12034,12 +12444,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2003-06-01</t>
+          <t>2003-04-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2003-06</t>
+          <t>2003-04</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -12169,12 +12579,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>2003-05-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2003-07</t>
+          <t>2003-05</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -12307,22 +12717,22 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>2003-05-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2003-07</t>
+          <t>2003-05</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>0.002104635732751713</v>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
@@ -12442,12 +12852,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2003-06-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2003-08</t>
+          <t>2003-06</t>
         </is>
       </c>
       <c r="N84" t="n">
@@ -12580,12 +12990,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2003-06-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2003-08</t>
+          <t>2003-06</t>
         </is>
       </c>
       <c r="N85" t="n">
@@ -12715,12 +13125,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2003-09-01</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2003-09</t>
+          <t>2003-07</t>
         </is>
       </c>
       <c r="N86" t="n">
@@ -12853,12 +13263,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2003-09-01</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2003-09</t>
+          <t>2003-07</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -12988,12 +13398,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2003-10</t>
+          <t>2003-08</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -13126,12 +13536,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2003-10</t>
+          <t>2003-08</t>
         </is>
       </c>
       <c r="N89" t="n">
@@ -13261,12 +13671,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2003-09-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2003-11</t>
+          <t>2003-09</t>
         </is>
       </c>
       <c r="N90" t="n">
@@ -13399,12 +13809,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2003-09-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2003-11</t>
+          <t>2003-09</t>
         </is>
       </c>
       <c r="N91" t="n">
@@ -13534,12 +13944,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2003-12</t>
+          <t>2003-10</t>
         </is>
       </c>
       <c r="N92" t="n">
@@ -13672,12 +14082,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2003-12</t>
+          <t>2003-10</t>
         </is>
       </c>
       <c r="N93" t="n">
@@ -13777,12 +14187,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -13807,12 +14217,12 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-11</t>
         </is>
       </c>
       <c r="N94" t="n">
@@ -13821,90 +14231,69 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ94" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13931,17 +14320,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -13966,12 +14355,12 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-11</t>
         </is>
       </c>
       <c r="N95" t="n">
@@ -13980,165 +14369,66 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+      <c r="R95" t="n">
+        <v>0</v>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD95" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE95" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF95" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG95" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN95" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -14200,12 +14490,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-12-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-12</t>
         </is>
       </c>
       <c r="N96" t="n">
@@ -14338,12 +14628,12 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-12-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-12</t>
         </is>
       </c>
       <c r="N97" t="n">
@@ -14443,12 +14733,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -14473,12 +14763,12 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2004-02-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2004-02</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N98" t="n">
@@ -14487,69 +14777,90 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14576,17 +14887,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -14611,12 +14922,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2004-02-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2004-02</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N99" t="n">
@@ -14625,66 +14936,165 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="R99" t="n">
-        <v>0</v>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN99" t="b">
+        <v>1</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D98_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14746,12 +15156,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2004-03</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N100" t="n">
@@ -14849,17 +15259,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -14884,12 +15294,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2004-03</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N101" t="n">
@@ -14898,66 +15308,170 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="R101" t="n">
-        <v>0</v>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_RABIES_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Hundaæði</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN101" t="b">
+        <v>0</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr"/>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_RABI_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT101" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -14989,12 +15503,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -15019,21 +15533,18 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2004-04-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N102" t="n">
         <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" t="n">
         <v>0</v>
       </c>
       <c r="R102" t="n">
@@ -15060,42 +15571,42 @@
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -15127,12 +15638,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -15157,18 +15668,21 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2004-04-01</t>
+          <t>2004-02-01</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="N103" t="n">
         <v>0</v>
       </c>
       <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
@@ -15195,42 +15709,42 @@
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -15262,12 +15776,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -15292,21 +15806,18 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2004-05-01</t>
+          <t>2004-02-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="N104" t="n">
         <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q104" t="n">
         <v>0</v>
       </c>
       <c r="R104" t="n">
@@ -15333,42 +15844,42 @@
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -15400,12 +15911,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -15430,22 +15941,25 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2004-05-01</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="N105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>0.002096564599647205</v>
+        <v>0</v>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
@@ -15468,42 +15982,42 @@
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -15535,12 +16049,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>DE-BY</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bayern, Germany</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -15565,33 +16079,31 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2004-05-10</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>1</v>
-      </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
@@ -15599,52 +16111,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS106" t="inlineStr">
-        <is>
-          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
-        </is>
-      </c>
+      <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -15706,12 +16214,12 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2004-04-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="N107" t="n">
@@ -15844,12 +16352,12 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2004-04-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="N108" t="n">
@@ -15979,12 +16487,12 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N109" t="n">
@@ -16117,22 +16625,22 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>0.002096564599647205</v>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
@@ -16217,17 +16725,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -16252,83 +16760,182 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2004-05-10</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2004-08</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
-      <c r="R111" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P111" t="n">
+        <v>1</v>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>__source_native__</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>national_ifsG_notification_registry</t>
+        </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>sha256:8ea6da325480416acd58134f28e2e53f4fa75aee022f37cce74fbc56eaa1a145</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>DE_RKI_SURVSTAT_source_native</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN111" t="b">
+        <v>0</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_RABI_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT111" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -16360,12 +16967,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>DE-BY</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Bayern, Germany</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -16390,80 +16997,101 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2004-05-10</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2004-08</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
+      </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16490,17 +17118,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE-BY</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Bayern, Germany</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -16525,83 +17153,179 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2004-09-01</t>
+          <t>2004-05-10</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2004-09</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
-      <c r="R113" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>tollwut</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>Tollwut</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>country:DE-BY:national</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL113" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN113" t="b">
+        <v>1</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>HOLD_DE_75ce880a8558ac5ed506cb9be3d0</t>
+        </is>
+      </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16633,12 +17357,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -16663,18 +17387,21 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2004-09-01</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2004-09</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N114" t="n">
         <v>0</v>
       </c>
       <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
@@ -16701,42 +17428,42 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -16768,12 +17495,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -16798,21 +17525,18 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2004-10-01</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2004-10</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N115" t="n">
         <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
@@ -16839,42 +17563,42 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -16906,12 +17630,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -16936,18 +17660,21 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2004-10-01</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2004-10</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="N116" t="n">
         <v>0</v>
       </c>
       <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
@@ -16974,42 +17701,42 @@
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17041,12 +17768,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -17071,21 +17798,18 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2004-11-01</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2004-11</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="N117" t="n">
         <v>0</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
@@ -17112,42 +17836,42 @@
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17179,12 +17903,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -17209,18 +17933,21 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2004-11-01</t>
+          <t>2004-08-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2004-11</t>
+          <t>2004-08</t>
         </is>
       </c>
       <c r="N118" t="n">
         <v>0</v>
       </c>
       <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
@@ -17247,42 +17974,42 @@
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17314,12 +18041,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -17344,21 +18071,18 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-08-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2004-08</t>
         </is>
       </c>
       <c r="N119" t="n">
         <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
@@ -17385,42 +18109,42 @@
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17452,12 +18176,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -17482,18 +18206,21 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-09-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2004-09</t>
         </is>
       </c>
       <c r="N120" t="n">
         <v>0</v>
       </c>
       <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
@@ -17520,40 +18247,994 @@
       </c>
       <c r="AV120" t="inlineStr">
         <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2004-09-01</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2004-09</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
+      <c r="AT121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW120" t="inlineStr">
+      <c r="AW121" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
+      <c r="AX121" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY120" t="inlineStr">
+      <c r="AY121" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
+      <c r="AZ121" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA120" t="inlineStr">
+      <c r="BA121" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB120" t="inlineStr">
+      <c r="BB121" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC120" t="inlineStr">
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2004-10-01</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2004-10</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
+      <c r="AT122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2004-10-01</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2004-10</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
+      <c r="AT123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2004-11-01</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2004-11</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
+      <c r="AT124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2004-11-01</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2004-11</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
+      <c r="AT125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2004-12</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr"/>
+      <c r="AT126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2004-12</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
+      <c r="AT127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -17685,7 +19366,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">
@@ -17705,7 +19386,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -17715,7 +19396,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d019/2000-2004.xlsx
+++ b/diseases/d019/2000-2004.xlsx
@@ -1164,6 +1164,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1176,12 +1181,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1541,6 +1556,11 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1553,12 +1573,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1679,6 +1709,11 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1691,12 +1726,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1817,6 +1862,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1829,12 +1879,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1955,6 +2015,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1967,12 +2032,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2093,6 +2168,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2105,12 +2185,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2231,6 +2321,11 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2243,12 +2338,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2369,6 +2474,11 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2381,12 +2491,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2507,6 +2627,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2519,12 +2644,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2645,6 +2780,11 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2657,12 +2797,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2783,6 +2933,11 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2795,12 +2950,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2921,6 +3086,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2933,12 +3103,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3452,6 +3632,11 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3464,12 +3649,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3826,6 +4021,11 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3838,12 +4038,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3964,6 +4174,11 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3976,12 +4191,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -4099,6 +4324,11 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4111,12 +4341,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4237,6 +4477,11 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4249,12 +4494,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4372,6 +4627,11 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4384,12 +4644,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4510,6 +4780,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4522,12 +4797,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4645,6 +4930,11 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4657,12 +4947,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4783,6 +5083,11 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4795,12 +5100,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4918,6 +5233,11 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4930,12 +5250,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5056,6 +5386,11 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5068,12 +5403,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5191,6 +5536,11 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5203,12 +5553,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5329,6 +5689,11 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5341,12 +5706,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5464,6 +5839,11 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5476,12 +5856,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5602,6 +5992,11 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5614,12 +6009,22 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5737,6 +6142,11 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5749,12 +6159,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5875,6 +6295,11 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5887,12 +6312,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6010,6 +6445,11 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6022,12 +6462,22 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6148,6 +6598,11 @@
       <c r="R38" t="n">
         <v>0.01476180680677245</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6160,12 +6615,22 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6283,6 +6748,11 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6295,12 +6765,22 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6421,6 +6901,11 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6433,12 +6918,22 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6556,6 +7051,11 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6568,12 +7068,22 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6694,6 +7204,11 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6706,12 +7221,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6829,6 +7354,11 @@
       <c r="R43" t="n">
         <v>0.002125693624458129</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6841,12 +7371,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7360,6 +7900,11 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7372,12 +7917,22 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7734,6 +8289,11 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7746,12 +8306,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7872,6 +8442,11 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7884,12 +8459,22 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8007,6 +8592,11 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8019,12 +8609,22 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8145,6 +8745,11 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8157,12 +8762,22 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8280,6 +8895,11 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8292,12 +8912,22 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8418,6 +9048,11 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8430,12 +9065,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8553,6 +9198,11 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8565,12 +9215,22 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8691,6 +9351,11 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8703,12 +9368,22 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8826,6 +9501,11 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8838,12 +9518,22 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8964,6 +9654,11 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8976,12 +9671,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9099,6 +9804,11 @@
       <c r="R58" t="n">
         <v>0.002114204216545633</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9111,12 +9821,22 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9237,6 +9957,11 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9249,12 +9974,22 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9372,6 +10107,11 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9384,12 +10124,22 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9510,6 +10260,11 @@
       <c r="R61" t="n">
         <v>0</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9522,12 +10277,22 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9645,6 +10410,11 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9657,12 +10427,22 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9783,6 +10563,11 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9795,12 +10580,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9918,6 +10713,11 @@
       <c r="R64" t="n">
         <v>0</v>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9930,12 +10730,22 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10056,6 +10866,11 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10068,12 +10883,22 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10191,6 +11016,11 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10203,12 +11033,22 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10329,6 +11169,11 @@
       <c r="R67" t="n">
         <v>0</v>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10341,12 +11186,22 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10464,6 +11319,11 @@
       <c r="R68" t="n">
         <v>0</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10476,12 +11336,22 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10602,6 +11472,11 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10614,12 +11489,22 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10737,6 +11622,11 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10749,12 +11639,22 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -11268,6 +12168,11 @@
       <c r="R73" t="n">
         <v>0</v>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11280,12 +12185,22 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11642,6 +12557,11 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11654,12 +12574,22 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -11780,6 +12710,11 @@
       <c r="R76" t="n">
         <v>0</v>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11792,12 +12727,22 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -11915,6 +12860,11 @@
       <c r="R77" t="n">
         <v>0.002104635732751713</v>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11927,12 +12877,22 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -12053,6 +13013,11 @@
       <c r="R78" t="n">
         <v>0</v>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12065,12 +13030,22 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -12188,6 +13163,11 @@
       <c r="R79" t="n">
         <v>0</v>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12200,12 +13180,22 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12326,6 +13316,11 @@
       <c r="R80" t="n">
         <v>0</v>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12338,12 +13333,22 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12461,6 +13466,11 @@
       <c r="R81" t="n">
         <v>0</v>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12473,12 +13483,22 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12599,6 +13619,11 @@
       <c r="R82" t="n">
         <v>0</v>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12611,12 +13636,22 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -12734,6 +13769,11 @@
       <c r="R83" t="n">
         <v>0.002104635732751713</v>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12746,12 +13786,22 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -12872,6 +13922,11 @@
       <c r="R84" t="n">
         <v>0</v>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12884,12 +13939,22 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -13007,6 +14072,11 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13019,12 +14089,22 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -13145,6 +14225,11 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13157,12 +14242,22 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -13280,6 +14375,11 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13292,12 +14392,22 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -13418,6 +14528,11 @@
       <c r="R88" t="n">
         <v>0</v>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13430,12 +14545,22 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -13553,6 +14678,11 @@
       <c r="R89" t="n">
         <v>0</v>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13565,12 +14695,22 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -13691,6 +14831,11 @@
       <c r="R90" t="n">
         <v>0</v>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13703,12 +14848,22 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -13826,6 +14981,11 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13838,12 +14998,22 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -13964,6 +15134,11 @@
       <c r="R92" t="n">
         <v>0</v>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13976,12 +15151,22 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -14099,6 +15284,11 @@
       <c r="R93" t="n">
         <v>0</v>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14111,12 +15301,22 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -14237,6 +15437,11 @@
       <c r="R94" t="n">
         <v>0</v>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14249,12 +15454,22 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -14372,6 +15587,11 @@
       <c r="R95" t="n">
         <v>0</v>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14384,12 +15604,22 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -14510,6 +15740,11 @@
       <c r="R96" t="n">
         <v>0</v>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14522,12 +15757,22 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -14645,6 +15890,11 @@
       <c r="R97" t="n">
         <v>0</v>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14657,12 +15907,22 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -15176,6 +16436,11 @@
       <c r="R100" t="n">
         <v>0</v>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15188,12 +16453,22 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -15550,6 +16825,11 @@
       <c r="R102" t="n">
         <v>0</v>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15562,12 +16842,22 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -15688,6 +16978,11 @@
       <c r="R103" t="n">
         <v>0</v>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15700,12 +16995,22 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -15823,6 +17128,11 @@
       <c r="R104" t="n">
         <v>0</v>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15835,12 +17145,22 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -15961,6 +17281,11 @@
       <c r="R105" t="n">
         <v>0</v>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15973,12 +17298,22 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -16096,6 +17431,11 @@
       <c r="R106" t="n">
         <v>0</v>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16108,12 +17448,22 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -16234,6 +17584,11 @@
       <c r="R107" t="n">
         <v>0</v>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16246,12 +17601,22 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -16369,6 +17734,11 @@
       <c r="R108" t="n">
         <v>0</v>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16381,12 +17751,22 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -16507,6 +17887,11 @@
       <c r="R109" t="n">
         <v>0</v>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16519,12 +17904,22 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -16642,6 +18037,11 @@
       <c r="R110" t="n">
         <v>0.002096564599647205</v>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16654,12 +18054,22 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -17407,6 +18817,11 @@
       <c r="R114" t="n">
         <v>0</v>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17419,12 +18834,22 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
         <v>0</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -17542,6 +18967,11 @@
       <c r="R115" t="n">
         <v>0</v>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17554,12 +18984,22 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -17680,6 +19120,11 @@
       <c r="R116" t="n">
         <v>0</v>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17692,12 +19137,22 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -17815,6 +19270,11 @@
       <c r="R117" t="n">
         <v>0</v>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17827,12 +19287,22 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -17953,6 +19423,11 @@
       <c r="R118" t="n">
         <v>0</v>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17965,12 +19440,22 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -18088,6 +19573,11 @@
       <c r="R119" t="n">
         <v>0</v>
       </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18100,12 +19590,22 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -18226,6 +19726,11 @@
       <c r="R120" t="n">
         <v>0</v>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18238,12 +19743,22 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -18361,6 +19876,11 @@
       <c r="R121" t="n">
         <v>0</v>
       </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18373,12 +19893,22 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -18499,6 +20029,11 @@
       <c r="R122" t="n">
         <v>0</v>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18511,12 +20046,22 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -18634,6 +20179,11 @@
       <c r="R123" t="n">
         <v>0</v>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18646,12 +20196,22 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -18772,6 +20332,11 @@
       <c r="R124" t="n">
         <v>0</v>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18784,12 +20349,22 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -18907,6 +20482,11 @@
       <c r="R125" t="n">
         <v>0</v>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18919,12 +20499,22 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -19045,6 +20635,11 @@
       <c r="R126" t="n">
         <v>0</v>
       </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19057,12 +20652,22 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -19180,6 +20785,11 @@
       <c r="R127" t="n">
         <v>0</v>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19192,12 +20802,22 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
